--- a/artfynd/A 10368-2022 artfynd.xlsx
+++ b/artfynd/A 10368-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 10368-2022 artfynd.xlsx
+++ b/artfynd/A 10368-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1900233</v>
+        <v>89970</v>
       </c>
       <c r="B2" t="n">
-        <v>78568</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>687943.3952763975</v>
+        <v>687943</v>
       </c>
       <c r="R2" t="n">
-        <v>6644034.08827469</v>
+        <v>6644034</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,21 +743,11 @@
           <t>2007-10-23</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2007-10-23</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -779,7 +764,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asplåga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -797,53 +782,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1900232</v>
+        <v>75541653</v>
       </c>
       <c r="B3" t="n">
-        <v>78568</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81025</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>738</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sw.) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Herrgården, Upl</t>
+          <t>Aspbladmossen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>688058.3550541773</v>
+        <v>688082</v>
       </c>
       <c r="R3" t="n">
-        <v>6644021.326964483</v>
+        <v>6644004</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,22 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2007-10-23</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2007-10-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,74 +863,73 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Gårdsmiljö med hamlade träd och alleträd</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Maria Jakobsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Olle Finnström, Barbara Kühn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89970</v>
+        <v>115916082</v>
       </c>
       <c r="B4" t="n">
-        <v>94120</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81025</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>738</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Sw.) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Herrgården, V om torpet, utmed grusvägen, Upl</t>
+          <t>Herrgården, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>687943.3952763975</v>
+        <v>688079</v>
       </c>
       <c r="R4" t="n">
-        <v>6644034.08827469</v>
+        <v>6644004</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,22 +953,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2007-10-23</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2007-10-23</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>5 dm2 på ask. 150 cm diameter.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,79 +984,64 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Hygge med lämnade lövträd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>asplåga</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Viktor Lund, Kristoffer Stighäll, Mats Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1999983</v>
+        <v>74811034</v>
       </c>
       <c r="B5" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83315</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>1469</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Liten blekspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Sclerophora peronella</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Herrgården, V om torpet, utmed grusvägen, Upl</t>
+          <t>Herrgården vid sjön Sottern, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>687943.3952763975</v>
+        <v>688069</v>
       </c>
       <c r="R5" t="n">
-        <v>6644034.08827469</v>
+        <v>6644028</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1106,22 +1065,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2007-10-23</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1997-10-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2007-10-23</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1997-10-14</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På naken ved på grov, levande lönn.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,74 +1087,81 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Hygge med lämnade lövträd</t>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>Skogslönn</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Naken ved på grov, levande lönn. # Skogslönn</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104932720</v>
+        <v>104940071</v>
       </c>
       <c r="B6" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92292</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>1506</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Sacc.) Ginns</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Aspbladsmossen N, 250 m V Herrgården, Upl</t>
+          <t>Aspbladsmossen NR, skogsbäck SV Herrgården, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>687920.2071890663</v>
+        <v>688000</v>
       </c>
       <c r="R6" t="n">
-        <v>6644044.47341214</v>
+        <v>6643930</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1230,19 +1191,9 @@
           <t>2022-12-04</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-12-04</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1263,44 +1214,39 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Rikard Anderberg, Maya Edlund, Fingal Gyllang</t>
+          <t>Rikard Anderberg, Maya Edlund, Fingal Gyllang, Magnus Nilsson, Malin Löfgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104932412</v>
+        <v>104940023</v>
       </c>
       <c r="B7" t="n">
-        <v>100515</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97812</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>223246</v>
+        <v>2605</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Stenporella</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Porella cordaeana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>(Huebener) Moore</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1310,14 +1256,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Aspbladsmossen N, 250 m V Herrgården, Upl</t>
+          <t>Aspbladsmossen NR, skogsbäck SV Herrgården, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>687920.2071890663</v>
+        <v>688000</v>
       </c>
       <c r="R7" t="n">
-        <v>6644044.47341214</v>
+        <v>6643930</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1347,19 +1293,9 @@
           <t>2022-12-04</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-12-04</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1387,15 +1323,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104932759</v>
+        <v>104932408</v>
       </c>
       <c r="B8" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1403,30 +1334,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229497</v>
+        <v>2667</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>med isidier</t>
-        </is>
-      </c>
+          <t>utan kapsel</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1434,10 +1366,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>687925.7530015949</v>
+        <v>687920</v>
       </c>
       <c r="R8" t="n">
-        <v>6644014.591734299</v>
+        <v>6644045</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1467,19 +1399,9 @@
           <t>2022-12-04</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-12-04</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1507,15 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104932405</v>
+        <v>104940072</v>
       </c>
       <c r="B9" t="n">
-        <v>92939</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96441</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1523,21 +1440,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2779</v>
+        <v>2668</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1547,14 +1464,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Aspbladsmossen N, 250 m V Herrgården, Upl</t>
+          <t>Aspbladsmossen NR, skogsbäck SV Herrgården, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>687920.2071890663</v>
+        <v>688000</v>
       </c>
       <c r="R9" t="n">
-        <v>6644044.47341214</v>
+        <v>6643930</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1584,19 +1501,9 @@
           <t>2022-12-04</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-12-04</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1624,46 +1531,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104932402</v>
+        <v>104932404</v>
       </c>
       <c r="B10" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>2671</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1671,10 +1570,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>687920.2071890663</v>
+        <v>687920</v>
       </c>
       <c r="R10" t="n">
-        <v>6644044.47341214</v>
+        <v>6644045</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1704,19 +1603,9 @@
           <t>2022-12-04</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-12-04</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1744,15 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104932417</v>
+        <v>104939956</v>
       </c>
       <c r="B11" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1760,21 +1644,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2809</v>
+        <v>2675</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Piskbaronmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Pseudanomodon attenuatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Hedw.) Ignatov &amp; Fedosov</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1784,14 +1668,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Aspbladsmossen N, 250 m V Herrgården, Upl</t>
+          <t>Aspbladsmossen NR, skogsbäck SV Herrgården, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>687920.2071890663</v>
+        <v>688000</v>
       </c>
       <c r="R11" t="n">
-        <v>6644044.47341214</v>
+        <v>6643930</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1821,19 +1705,9 @@
           <t>2022-12-04</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-12-04</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1854,22 +1728,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Rikard Anderberg, Maya Edlund, Fingal Gyllang, Malin Löfgren</t>
+          <t>Rikard Anderberg, Maya Edlund, Fingal Gyllang, Magnus Nilsson, Malin Löfgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>104932408</v>
+        <v>104932405</v>
       </c>
       <c r="B12" t="n">
-        <v>93145</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96231</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1877,30 +1746,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2667</v>
+        <v>2779</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neckera complanata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Huebener</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>utan kapsel</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -1909,10 +1774,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>687920.2071890663</v>
+        <v>687920</v>
       </c>
       <c r="R12" t="n">
-        <v>6644044.47341214</v>
+        <v>6644045</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1942,19 +1807,9 @@
           <t>2022-12-04</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-12-04</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1982,15 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>104932404</v>
+        <v>104932417</v>
       </c>
       <c r="B13" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1998,21 +1848,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2671</v>
+        <v>2809</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2026,10 +1876,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>687920.2071890663</v>
+        <v>687920</v>
       </c>
       <c r="R13" t="n">
-        <v>6644044.47341214</v>
+        <v>6644045</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2059,19 +1909,9 @@
           <t>2022-12-04</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-12-04</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2092,64 +1932,52 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Rikard Anderberg, Maya Edlund, Fingal Gyllang, Magnus Nilsson, Malin Löfgren</t>
+          <t>Rikard Anderberg, Maya Edlund, Fingal Gyllang, Malin Löfgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>104932756</v>
+        <v>1900232</v>
       </c>
       <c r="B14" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Aspbladsmossen N, 250 m V Herrgården, Upl</t>
+          <t>Herrgården, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>687925.7530015949</v>
+        <v>688058</v>
       </c>
       <c r="R14" t="n">
-        <v>6644014.591734299</v>
+        <v>6644021</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2176,22 +2004,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-12-04</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-12-04</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2200,22 +2018,1254 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Gårdsmiljö med hamlade träd och alleträd</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1900233</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Herrgården, V om torpet, utmed grusvägen, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>687943</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6644034</v>
+      </c>
+      <c r="S15" t="n">
+        <v>50</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Knutby</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2007-10-23</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2007-10-23</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Hygge med lämnade lövträd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>75541767</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Aspbladmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>688083</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6644013</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Knutby</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2018-09-27</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2018-09-27</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Maria Jakobsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Olle Finnström, Barbara Kühn</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>104932402</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Aspbladsmossen N, 250 m V Herrgården, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>687920</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6644045</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Knutby</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2022-12-04</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2022-12-04</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
           <t>Rikard Anderberg</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
+      <c r="AX17" t="inlineStr">
         <is>
           <t>Rikard Anderberg, Maya Edlund, Fingal Gyllang, Magnus Nilsson, Malin Löfgren</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>104932756</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Aspbladsmossen N, 250 m V Herrgården, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>687925</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6644015</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Knutby</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2022-12-04</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2022-12-04</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Rikard Anderberg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Rikard Anderberg, Maya Edlund, Fingal Gyllang, Magnus Nilsson, Malin Löfgren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1999983</v>
+      </c>
+      <c r="B19" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Herrgården, V om torpet, utmed grusvägen, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>687943</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6644034</v>
+      </c>
+      <c r="S19" t="n">
+        <v>50</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Knutby</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2007-10-23</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2007-10-23</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Hygge med lämnade lövträd</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2585357</v>
+      </c>
+      <c r="B20" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Knutby sn, S om Sotter nära Herrgården, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>688084</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6643970</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Knutby</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2005-09-30</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2005-09-30</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>skogsbilväg</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>3433608</v>
+      </c>
+      <c r="B21" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Knutby sn, S om Sotter nära Herrgården, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>688084</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6643970</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Knutby</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2005-09-30</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2005-09-30</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>skogsbilväg</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>5022546</v>
+      </c>
+      <c r="B22" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Knutby sn, S om Sotter nära Herrgården, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>688084</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6643970</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Knutby</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2005-09-30</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2005-09-30</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>skogsbilväg</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>104932720</v>
+      </c>
+      <c r="B23" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Aspbladsmossen N, 250 m V Herrgården, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>687920</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6644045</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Knutby</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2022-12-04</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2022-12-04</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Rikard Anderberg</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Rikard Anderberg, Maya Edlund, Fingal Gyllang</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>75541640</v>
+      </c>
+      <c r="B24" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Aspbladmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>688055</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6644055</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Knutby</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2018-09-27</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2018-09-27</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Maria Jakobsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Olle Finnström, Barbara Kühn</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>104932412</v>
+      </c>
+      <c r="B25" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Aspbladsmossen N, 250 m V Herrgården, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>687920</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6644045</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Knutby</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2022-12-04</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2022-12-04</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Rikard Anderberg</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Rikard Anderberg, Maya Edlund, Fingal Gyllang, Magnus Nilsson, Malin Löfgren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>104932759</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>med isidier</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Aspbladsmossen N, 250 m V Herrgården, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>687925</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6644015</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Knutby</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2022-12-04</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2022-12-04</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Rikard Anderberg</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Rikard Anderberg, Maya Edlund, Fingal Gyllang, Magnus Nilsson, Malin Löfgren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
